--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3605" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="323">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -268,6 +268,10 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">fr-historique-des-actes-entries:La section contient au moins une entrée Acte (procedure). {entry.where(procedure.exists()).count() &gt;= 1}
+</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -813,111 +817,68 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t>Entrées Acte (procedure, 1..*) et Références externes (act, 0..*)</t>
+  </si>
+  <si>
+    <t>Section.entry.nullFlavor</t>
+  </si>
+  <si>
+    <t>Section.entry.realmCode</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.displayable</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.root</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.extension</t>
+  </si>
+  <si>
+    <t>Section.entry.templateId</t>
+  </si>
+  <si>
+    <t>Section.entry.typeCode</t>
+  </si>
+  <si>
+    <t>COMP</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-xActRelationshipEntry|3.0.0</t>
+  </si>
+  <si>
+    <t>Entry.typeCode</t>
+  </si>
+  <si>
+    <t>Section.entry.contextConductionInd</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Entry.contextConductionInd</t>
+  </si>
+  <si>
+    <t>Section.entry.act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-references-externes|0.1.0}
 </t>
   </si>
   <si>
-    <t>Section.entry:frActe</t>
-  </si>
-  <si>
-    <t>frActe</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry.typeCode</t>
-  </si>
-  <si>
-    <t>COMP</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-xActRelationshipEntry|3.0.0</t>
-  </si>
-  <si>
-    <t>Entry.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>Entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.act</t>
-  </si>
-  <si>
-    <t>Section.entry.act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act
-</t>
+    <t>Entrée Références externes</t>
   </si>
   <si>
     <t>Entry.act</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.encounter</t>
   </si>
   <si>
     <t>Section.entry.encounter</t>
@@ -930,9 +891,6 @@
     <t>Entry.encounter</t>
   </si>
   <si>
-    <t>Section.entry:frActe.observation</t>
-  </si>
-  <si>
     <t>Section.entry.observation</t>
   </si>
   <si>
@@ -943,9 +901,6 @@
     <t>Entry.observation</t>
   </si>
   <si>
-    <t>Section.entry:frActe.observationMedia</t>
-  </si>
-  <si>
     <t>Section.entry.observationMedia</t>
   </si>
   <si>
@@ -956,9 +911,6 @@
     <t>Entry.observationMedia</t>
   </si>
   <si>
-    <t>Section.entry:frActe.organizer</t>
-  </si>
-  <si>
     <t>Section.entry.organizer</t>
   </si>
   <si>
@@ -969,9 +921,6 @@
     <t>Entry.organizer</t>
   </si>
   <si>
-    <t>Section.entry:frActe.procedure</t>
-  </si>
-  <si>
     <t>Section.entry.procedure</t>
   </si>
   <si>
@@ -985,9 +934,6 @@
     <t>Entry.procedure</t>
   </si>
   <si>
-    <t>Section.entry:frActe.regionOfInterest</t>
-  </si>
-  <si>
     <t>Section.entry.regionOfInterest</t>
   </si>
   <si>
@@ -998,9 +944,6 @@
     <t>Entry.regionOfInterest</t>
   </si>
   <si>
-    <t>Section.entry:frActe.substanceAdministration</t>
-  </si>
-  <si>
     <t>Section.entry.substanceAdministration</t>
   </si>
   <si>
@@ -1011,9 +954,6 @@
     <t>Entry.substanceAdministration</t>
   </si>
   <si>
-    <t>Section.entry:frActe.supply</t>
-  </si>
-  <si>
     <t>Section.entry.supply</t>
   </si>
   <si>
@@ -1022,83 +962,6 @@
   </si>
   <si>
     <t>Entry.supply</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes</t>
-  </si>
-  <si>
-    <t>frReferencesExternes</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-references-externes|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Entrée Références externes</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.encounter</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.observationMedia</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.organizer</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.procedure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Procedure
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.supply</t>
   </si>
   <si>
     <t>Section.component</t>
@@ -1471,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK114"/>
+  <dimension ref="A1:AK92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.46484375" customWidth="true" bestFit="true"/>
@@ -1722,25 +1585,25 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>81</v>
@@ -1758,11 +1621,11 @@
         <v>75</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1789,11 +1652,11 @@
         <v>75</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>75</v>
@@ -1811,7 +1674,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>81</v>
@@ -1831,10 +1694,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1857,11 +1720,11 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1912,7 +1775,7 @@
         <v>75</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>81</v>
@@ -1932,10 +1795,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1958,11 +1821,11 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2013,7 +1876,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>81</v>
@@ -2025,7 +1888,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
@@ -2033,17 +1896,17 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>81</v>
@@ -2061,11 +1924,11 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2092,11 +1955,11 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>75</v>
@@ -2114,7 +1977,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>81</v>
@@ -2134,17 +1997,17 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>81</v>
@@ -2162,11 +2025,11 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2217,7 +2080,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>81</v>
@@ -2237,17 +2100,17 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>81</v>
@@ -2265,11 +2128,11 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2320,7 +2183,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
@@ -2340,17 +2203,17 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>76</v>
@@ -2368,11 +2231,11 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2381,7 +2244,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>75</v>
@@ -2423,7 +2286,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -2443,17 +2306,17 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>76</v>
@@ -2471,11 +2334,11 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2526,7 +2389,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -2546,10 +2409,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2557,10 +2420,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -2572,11 +2435,11 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2615,17 +2478,17 @@
         <v>75</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2645,13 +2508,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>75</v>
@@ -2673,13 +2536,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2730,7 +2593,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -2750,17 +2613,17 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>81</v>
@@ -2778,11 +2641,11 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2809,11 +2672,11 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2831,7 +2694,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -2851,17 +2714,17 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>81</v>
@@ -2879,11 +2742,11 @@
         <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2934,7 +2797,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -2954,17 +2817,17 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>81</v>
@@ -2982,11 +2845,11 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3037,7 +2900,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3057,17 +2920,17 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>76</v>
@@ -3085,11 +2948,11 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3101,7 +2964,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -3140,7 +3003,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3160,17 +3023,17 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>81</v>
@@ -3188,11 +3051,11 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3243,7 +3106,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3263,13 +3126,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>75</v>
@@ -3291,13 +3154,13 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3348,7 +3211,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3368,17 +3231,17 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>81</v>
@@ -3396,11 +3259,11 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3427,11 +3290,11 @@
         <v>75</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>75</v>
@@ -3449,7 +3312,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3469,17 +3332,17 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>81</v>
@@ -3497,11 +3360,11 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3552,7 +3415,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3572,17 +3435,17 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>81</v>
@@ -3600,11 +3463,11 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3655,7 +3518,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3675,17 +3538,17 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>76</v>
@@ -3703,11 +3566,11 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3719,7 +3582,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -3758,7 +3621,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -3778,17 +3641,17 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>81</v>
@@ -3806,11 +3669,11 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3861,7 +3724,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -3881,13 +3744,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3909,13 +3772,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3966,7 +3829,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -3986,17 +3849,17 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>81</v>
@@ -4014,11 +3877,11 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4045,11 +3908,11 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4067,7 +3930,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4087,17 +3950,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>81</v>
@@ -4115,11 +3978,11 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4170,7 +4033,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4190,17 +4053,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>81</v>
@@ -4218,11 +4081,11 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4273,7 +4136,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4293,17 +4156,17 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>76</v>
@@ -4321,11 +4184,11 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4337,7 +4200,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4376,7 +4239,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4396,17 +4259,17 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>81</v>
@@ -4424,11 +4287,11 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4479,7 +4342,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4499,13 +4362,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
@@ -4527,13 +4390,13 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4584,7 +4447,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -4604,17 +4467,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>81</v>
@@ -4632,11 +4495,11 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4663,11 +4526,11 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -4685,7 +4548,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4705,17 +4568,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>81</v>
@@ -4733,11 +4596,11 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4788,7 +4651,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -4808,17 +4671,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>81</v>
@@ -4836,11 +4699,11 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4891,7 +4754,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4911,17 +4774,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>76</v>
@@ -4939,11 +4802,11 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4955,7 +4818,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -4994,7 +4857,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5014,17 +4877,17 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>81</v>
@@ -5042,11 +4905,11 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5097,7 +4960,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5117,10 +4980,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5143,10 +5006,10 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -5198,7 +5061,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5218,10 +5081,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5244,7 +5107,7 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -5255,7 +5118,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>75</v>
@@ -5273,11 +5136,11 @@
         <v>75</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>75</v>
@@ -5295,7 +5158,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5315,10 +5178,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5341,7 +5204,7 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -5352,7 +5215,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>75</v>
@@ -5370,11 +5233,11 @@
         <v>75</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
@@ -5392,7 +5255,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5412,10 +5275,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5429,7 +5292,7 @@
         <v>76</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>75</v>
@@ -5438,13 +5301,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5495,7 +5358,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5515,10 +5378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5532,7 +5395,7 @@
         <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>75</v>
@@ -5541,13 +5404,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5598,7 +5461,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5618,17 +5481,17 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>81</v>
@@ -5646,11 +5509,11 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5677,11 +5540,11 @@
         <v>75</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>75</v>
@@ -5699,7 +5562,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5719,10 +5582,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5738,7 +5601,7 @@
         <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>75</v>
@@ -5747,11 +5610,11 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5763,7 +5626,7 @@
         <v>75</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>75</v>
@@ -5802,7 +5665,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -5822,17 +5685,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>76</v>
@@ -5841,7 +5704,7 @@
         <v>76</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>75</v>
@@ -5850,11 +5713,11 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5866,7 +5729,7 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>75</v>
@@ -5905,7 +5768,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -5925,17 +5788,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>81</v>
@@ -5953,11 +5816,11 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5969,7 +5832,7 @@
         <v>75</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>75</v>
@@ -6008,7 +5871,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6028,17 +5891,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -6056,11 +5919,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6111,7 +5974,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6131,17 +5994,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>76</v>
@@ -6150,7 +6013,7 @@
         <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -6159,11 +6022,11 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6175,7 +6038,7 @@
         <v>75</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>75</v>
@@ -6214,7 +6077,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6234,10 +6097,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6260,11 +6123,11 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6315,7 +6178,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6335,10 +6198,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6361,11 +6224,11 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6416,7 +6279,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6436,17 +6299,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>81</v>
@@ -6464,11 +6327,11 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6519,7 +6382,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -6539,17 +6402,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>81</v>
@@ -6567,11 +6430,11 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6622,7 +6485,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6642,17 +6505,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>81</v>
@@ -6670,11 +6533,11 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6725,7 +6588,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6745,10 +6608,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6762,7 +6625,7 @@
         <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>75</v>
@@ -6771,17 +6634,17 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -6830,7 +6693,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6850,10 +6713,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6867,7 +6730,7 @@
         <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>75</v>
@@ -6876,16 +6739,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6935,7 +6798,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -6955,10 +6818,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6981,15 +6844,15 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7038,7 +6901,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -7058,10 +6921,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7084,15 +6947,15 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7117,11 +6980,11 @@
         <v>75</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>75</v>
@@ -7139,7 +7002,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7159,10 +7022,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7185,17 +7048,17 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7244,7 +7107,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7264,10 +7127,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7290,13 +7153,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -7345,7 +7208,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7365,10 +7228,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7391,13 +7254,13 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
@@ -7446,7 +7309,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7464,12 +7327,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7483,7 +7346,7 @@
         <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>75</v>
@@ -7492,9 +7355,11 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="L59" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7533,17 +7398,19 @@
         <v>75</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7563,23 +7430,23 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C60" t="s" s="2">
         <v>260</v>
       </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>75</v>
@@ -7591,10 +7458,12 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>257</v>
+        <v>87</v>
       </c>
       <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
+      <c r="M60" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7620,13 +7489,11 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -7644,13 +7511,13 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>256</v>
+        <v>91</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>75</v>
@@ -7667,20 +7534,18 @@
         <v>261</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E61" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>75</v>
@@ -7692,11 +7557,11 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7723,11 +7588,13 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -7745,13 +7612,13 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>75</v>
@@ -7765,10 +7632,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7779,7 +7646,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -7791,11 +7658,11 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7846,19 +7713,19 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
@@ -7866,16 +7733,18 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F63" t="s" s="2">
         <v>81</v>
       </c>
@@ -7892,11 +7761,11 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7923,13 +7792,11 @@
         <v>75</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>75</v>
@@ -7947,7 +7814,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -7959,7 +7826,7 @@
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -7967,17 +7834,17 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>81</v>
@@ -7995,11 +7862,11 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8026,11 +7893,13 @@
         <v>75</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
@@ -8048,7 +7917,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8068,17 +7937,17 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>81</v>
@@ -8096,11 +7965,11 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8151,7 +8020,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8171,20 +8040,20 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>76</v>
@@ -8199,11 +8068,11 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8212,7 +8081,7 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>75</v>
@@ -8254,7 +8123,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8274,17 +8143,17 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>76</v>
@@ -8302,11 +8171,11 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8315,7 +8184,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>75</v>
@@ -8357,7 +8226,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8377,23 +8246,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E68" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>75</v>
@@ -8405,11 +8272,11 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8460,13 +8327,13 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>75</v>
@@ -8480,10 +8347,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8494,7 +8361,7 @@
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>75</v>
@@ -8506,16 +8373,14 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
@@ -8537,13 +8402,11 @@
         <v>75</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>75</v>
+        <v>271</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>75</v>
@@ -8561,13 +8424,13 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>126</v>
+        <v>272</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>75</v>
@@ -8581,10 +8444,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8607,18 +8470,18 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
-        <v>281</v>
+        <v>75</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>75</v>
+        <v>274</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>75</v>
@@ -8636,11 +8499,13 @@
         <v>75</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>282</v>
+        <v>75</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -8658,7 +8523,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -8678,10 +8543,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8704,9 +8569,11 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L71" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8715,7 +8582,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>286</v>
+        <v>75</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>75</v>
@@ -8757,7 +8624,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -8777,10 +8644,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8803,7 +8670,7 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8856,7 +8723,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -8876,10 +8743,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8902,7 +8769,7 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8955,7 +8822,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -8975,10 +8842,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9001,7 +8868,7 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -9054,7 +8921,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9074,10 +8941,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9100,7 +8967,7 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9153,7 +9020,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9173,10 +9040,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9199,9 +9066,11 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="L76" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9252,7 +9121,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9272,10 +9141,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9298,11 +9167,9 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9353,7 +9220,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -9373,10 +9240,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9399,7 +9266,7 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9452,7 +9319,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -9472,10 +9339,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9498,7 +9365,7 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9551,7 +9418,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9571,10 +9438,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9585,7 +9452,7 @@
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>75</v>
@@ -9597,12 +9464,16 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="L80" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
       </c>
@@ -9650,13 +9521,13 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>75</v>
@@ -9670,23 +9541,23 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E81" s="2"/>
+      <c r="E81" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>75</v>
@@ -9698,10 +9569,12 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>257</v>
+        <v>87</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9727,13 +9600,11 @@
         <v>75</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>75</v>
@@ -9751,13 +9622,13 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>256</v>
+        <v>91</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>75</v>
@@ -9771,23 +9642,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>262</v>
+        <v>310</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E82" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>75</v>
@@ -9799,11 +9668,11 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9830,11 +9699,13 @@
         <v>75</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>75</v>
@@ -9852,13 +9723,13 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>75</v>
@@ -9872,10 +9743,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9886,7 +9757,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>75</v>
@@ -9898,11 +9769,11 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9953,19 +9824,19 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>75</v>
@@ -9973,16 +9844,18 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E84" s="2"/>
+      <c r="E84" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F84" t="s" s="2">
         <v>81</v>
       </c>
@@ -9999,11 +9872,11 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10030,13 +9903,11 @@
         <v>75</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>75</v>
@@ -10054,7 +9925,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10066,7 +9937,7 @@
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
@@ -10074,17 +9945,17 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>81</v>
@@ -10102,11 +9973,11 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10133,11 +10004,13 @@
         <v>75</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>75</v>
@@ -10155,7 +10028,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10175,17 +10048,17 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>81</v>
@@ -10203,11 +10076,11 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10258,7 +10131,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -10278,20 +10151,20 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>76</v>
@@ -10306,11 +10179,11 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10319,7 +10192,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>75</v>
@@ -10361,7 +10234,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -10381,17 +10254,17 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>76</v>
@@ -10409,11 +10282,11 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10422,7 +10295,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>75</v>
@@ -10464,7 +10337,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10484,23 +10357,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>75</v>
@@ -10512,11 +10383,11 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10567,13 +10438,13 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>75</v>
@@ -10587,10 +10458,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>278</v>
+        <v>318</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10601,7 +10472,7 @@
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>75</v>
@@ -10613,11 +10484,11 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>123</v>
+        <v>319</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10626,7 +10497,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>75</v>
@@ -10668,13 +10539,13 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>126</v>
+        <v>318</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>75</v>
@@ -10688,10 +10559,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10714,18 +10585,18 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
-        <v>281</v>
+        <v>75</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>75</v>
+        <v>274</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>75</v>
@@ -10743,11 +10614,13 @@
         <v>75</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>282</v>
+        <v>75</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>75</v>
@@ -10765,7 +10638,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -10785,10 +10658,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10796,7 +10669,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>76</v>
@@ -10811,7 +10684,7 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>108</v>
+        <v>322</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10822,7 +10695,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>286</v>
+        <v>75</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>75</v>
@@ -10864,10 +10737,10 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
@@ -10882,2220 +10755,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="L97" s="2"/>
-      <c r="M97" s="2"/>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M102" s="2"/>
-      <c r="N102" s="2"/>
-      <c r="O102" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E103" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L103" s="2"/>
-      <c r="M103" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y103" s="2"/>
-      <c r="Z103" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L104" s="2"/>
-      <c r="M104" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L105" s="2"/>
-      <c r="M105" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E106" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L106" s="2"/>
-      <c r="M106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y106" s="2"/>
-      <c r="Z106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E107" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L107" s="2"/>
-      <c r="M107" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E108" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L108" s="2"/>
-      <c r="M108" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E109" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L109" s="2"/>
-      <c r="M109" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E110" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L110" s="2"/>
-      <c r="M110" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L111" s="2"/>
-      <c r="M111" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L112" s="2"/>
-      <c r="M112" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L113" s="2"/>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK114">
+  <autoFilter ref="A1:AK92">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13105,7 +10766,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
